--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_metropolitana.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_metropolitana.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="Total_Regional" sheetId="1" r:id="rId1"/>
     <sheet name="Por_Sexo" sheetId="2" r:id="rId2"/>
-    <sheet name="Por_Edad" sheetId="3" r:id="rId3"/>
+    <sheet name="Por_Prov" sheetId="3" r:id="rId3"/>
+    <sheet name="Por_Edad" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -353,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -364,19 +365,44 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Residentes</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Proyectada</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Cobertura</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Categoria_lbl</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Total
-Regional</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B2">
+        <v>7550140</v>
+      </c>
+      <c r="C2">
+        <v>8420729</v>
+      </c>
+      <c r="D2">
         <v>89.6613582980761</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -465,7 +491,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -476,7 +502,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Tramo_Edad</t>
+          <t>Provincia</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -503,17 +529,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0-14</t>
+          <t>Melipilla</t>
         </is>
       </c>
       <c r="C2">
-        <v>542704</v>
+        <v>220082</v>
       </c>
       <c r="D2">
-        <v>579327</v>
+        <v>223335</v>
       </c>
       <c r="E2">
-        <v>93.67835436635959</v>
+        <v>98.54344370564398</v>
       </c>
     </row>
     <row r="3">
@@ -524,17 +550,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15-29</t>
+          <t>Chacabuco</t>
         </is>
       </c>
       <c r="C3">
-        <v>1502997</v>
+        <v>304447</v>
       </c>
       <c r="D3">
-        <v>1747689</v>
+        <v>362884</v>
       </c>
       <c r="E3">
-        <v>85.99911082578193</v>
+        <v>83.89650687271966</v>
       </c>
     </row>
     <row r="4">
@@ -545,17 +571,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30-44</t>
+          <t>Talagante</t>
         </is>
       </c>
       <c r="C4">
-        <v>1909303</v>
+        <v>342292</v>
       </c>
       <c r="D4">
-        <v>2123257</v>
+        <v>358723</v>
       </c>
       <c r="E4">
-        <v>89.92331121479877</v>
+        <v>95.41958558553536</v>
       </c>
     </row>
     <row r="5">
@@ -566,17 +592,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45-64</t>
+          <t>Maipo</t>
         </is>
       </c>
       <c r="C5">
-        <v>1854015</v>
+        <v>544674</v>
       </c>
       <c r="D5">
-        <v>1968542</v>
+        <v>585222</v>
       </c>
       <c r="E5">
-        <v>94.18214089412366</v>
+        <v>93.07134728359495</v>
       </c>
     </row>
     <row r="6">
@@ -587,17 +613,432 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>65+</t>
+          <t>Cordillera</t>
         </is>
       </c>
       <c r="C6">
-        <v>1073165</v>
+        <v>613262</v>
       </c>
       <c r="D6">
-        <v>1053991</v>
+        <v>720444</v>
       </c>
       <c r="E6">
-        <v>101.8191806191894</v>
+        <v>85.12278539345182</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>5525383</v>
+      </c>
+      <c r="D7">
+        <v>6170121</v>
+      </c>
+      <c r="E7">
+        <v>89.55064252386623</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Desagregación 1</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Tramo_Edad</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Residentes</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Proyectada</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Cobertura</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>34622</v>
+      </c>
+      <c r="D2">
+        <v>38905</v>
+      </c>
+      <c r="E2">
+        <v>88.9911322452127</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>5-9</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>33181</v>
+      </c>
+      <c r="D3">
+        <v>33883</v>
+      </c>
+      <c r="E3">
+        <v>97.92816456630169</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>10-14</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>474901</v>
+      </c>
+      <c r="D4">
+        <v>506539</v>
+      </c>
+      <c r="E4">
+        <v>93.7540840882933</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>15-19</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>464111</v>
+      </c>
+      <c r="D5">
+        <v>499699</v>
+      </c>
+      <c r="E5">
+        <v>92.87811262379952</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20-24</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>472416</v>
+      </c>
+      <c r="D6">
+        <v>561647</v>
+      </c>
+      <c r="E6">
+        <v>84.11261878012346</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>25-29</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>566470</v>
+      </c>
+      <c r="D7">
+        <v>686343</v>
+      </c>
+      <c r="E7">
+        <v>82.53453448203012</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>30-34</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>685115</v>
+      </c>
+      <c r="D8">
+        <v>786691</v>
+      </c>
+      <c r="E8">
+        <v>87.08819600071692</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>35-39</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>657041</v>
+      </c>
+      <c r="D9">
+        <v>718350</v>
+      </c>
+      <c r="E9">
+        <v>91.46530242917798</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>40-44</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>567147</v>
+      </c>
+      <c r="D10">
+        <v>618216</v>
+      </c>
+      <c r="E10">
+        <v>91.73929500368803</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>45-49</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>486599</v>
+      </c>
+      <c r="D11">
+        <v>563433</v>
+      </c>
+      <c r="E11">
+        <v>86.36324105971784</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>50-54</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>481331</v>
+      </c>
+      <c r="D12">
+        <v>501928</v>
+      </c>
+      <c r="E12">
+        <v>95.89642339140275</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>55-59</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>449440</v>
+      </c>
+      <c r="D13">
+        <v>475433</v>
+      </c>
+      <c r="E13">
+        <v>94.53277328246041</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>60-64</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>436645</v>
+      </c>
+      <c r="D14">
+        <v>427748</v>
+      </c>
+      <c r="E14">
+        <v>102.0799629688508</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>65-69</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>356552</v>
+      </c>
+      <c r="D15">
+        <v>357370</v>
+      </c>
+      <c r="E15">
+        <v>99.77110557685313</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>70-74</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>256293</v>
+      </c>
+      <c r="D16">
+        <v>277144</v>
+      </c>
+      <c r="E16">
+        <v>92.47647432381723</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>75-79</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>197480</v>
+      </c>
+      <c r="D17">
+        <v>184492</v>
+      </c>
+      <c r="E17">
+        <v>107.0398716475511</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>80+</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>262840</v>
+      </c>
+      <c r="D18">
+        <v>234985</v>
+      </c>
+      <c r="E18">
+        <v>111.8539481243484</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_metropolitana.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_metropolitana.xlsx
@@ -418,7 +418,7 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Desagregación 1</t>
+          <t>region</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Desagregación 1</t>
+          <t>region</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -660,7 +660,7 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Desagregación 1</t>
+          <t>region</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_metropolitana.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_metropolitana.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t xml:space="preserve">Categoria</t>
   </si>
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 21:15</t>
+    <t xml:space="preserve">2026-08-07 07:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -60,16 +60,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_regional_cobertura_2024_metropolitana.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Cobertura de residentes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Region de Metropolitana</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024</t>
   </si>
   <si>
     <t xml:space="preserve">region</t>
@@ -618,23 +627,23 @@
         <v>14</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -657,10 +666,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -674,10 +683,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>3704648</v>
@@ -691,10 +700,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>3845492</v>
@@ -727,10 +736,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -744,10 +753,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>220082</v>
@@ -761,10 +770,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>304447</v>
@@ -778,10 +787,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>342292</v>
@@ -795,10 +804,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>544674</v>
@@ -812,10 +821,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>613262</v>
@@ -829,10 +838,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>5525383</v>
@@ -865,10 +874,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -882,10 +891,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>34622</v>
@@ -899,10 +908,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>33181</v>
@@ -916,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>474901</v>
@@ -933,10 +942,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>464111</v>
@@ -950,10 +959,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>472416</v>
@@ -967,10 +976,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>566470</v>
@@ -984,10 +993,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>685115</v>
@@ -1001,10 +1010,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>657041</v>
@@ -1018,10 +1027,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>567147</v>
@@ -1035,10 +1044,10 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>486599</v>
@@ -1052,10 +1061,10 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>481331</v>
@@ -1069,10 +1078,10 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>449440</v>
@@ -1086,10 +1095,10 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>436645</v>
@@ -1103,10 +1112,10 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>356552</v>
@@ -1120,10 +1129,10 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>256293</v>
@@ -1137,10 +1146,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>197480</v>
@@ -1154,10 +1163,10 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>262840</v>

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_metropolitana.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_metropolitana.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-07 07:13</t>
+    <t xml:space="preserve">2026-08-28 11:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -897,13 +897,13 @@
         <v>33</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>34622</v>
+        <v>293724</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>38905</v>
+        <v>519713</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>88.99</v>
+        <v>56.52</v>
       </c>
     </row>
     <row r="3">
@@ -914,13 +914,13 @@
         <v>34</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>33181</v>
+        <v>442035</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>33883</v>
+        <v>500998</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>97.93</v>
+        <v>88.23</v>
       </c>
     </row>
     <row r="4">

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_metropolitana.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_metropolitana.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:14</t>
+    <t xml:space="preserve">2026-09-01 13:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_metropolitana.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_metropolitana.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-01 13:23</t>
+    <t xml:space="preserve">2026-09-06 17:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_metropolitana.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_metropolitana.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:20</t>
+    <t xml:space="preserve">2026-09-08 13:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
